--- a/data/trans_camb/IP16B02-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16B02-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-35,58; 0,0</t>
+          <t>-33,26; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-60,8; -7,23</t>
+          <t>-65,26; -7,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-34,0; 0,0</t>
+          <t>-39,83; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-40,65; 0,0</t>
+          <t>-37,18; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 0,0</t>
+          <t>-24,27; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-39,16; -7,02</t>
+          <t>-38,98; -7,51</t>
         </is>
       </c>
     </row>
@@ -707,39 +707,39 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,58; 0,0</t>
+          <t>-33,26; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-60,8; -7,23</t>
+          <t>-65,26; -7,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,0; 0,0</t>
+          <t>-39,83; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,65; 0,0</t>
+          <t>-37,18; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 0,0</t>
+          <t>-24,27; 0,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,16; -7,02</t>
+          <t>-38,98; -7,51</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -787,17 +787,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-39,55; -4,41</t>
+          <t>-38,1; -4,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-34,55; 0,0</t>
+          <t>-34,84; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-29,15; -3,56</t>
+          <t>-28,25; -3,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-26,18; -6,05</t>
+          <t>-25,9; -6,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 0,0</t>
+          <t>-16,68; 0,0</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,55; -4,41</t>
+          <t>-38,1; -4,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-34,55; 0,0</t>
+          <t>-34,84; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,15; -3,56</t>
+          <t>-28,25; -3,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,19 +883,19 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,18; -6,05</t>
+          <t>-25,9; -6,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 0,0</t>
+          <t>-16,68; 0,0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-23,68; 92,09</t>
+          <t>-22,3; 93,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-30,96; 0,0</t>
+          <t>-36,41; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-76,27; 0,0</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 33,65</t>
+          <t>-17,72; 36,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,69; 35,83</t>
+          <t>-25,43; 34,99</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,95; —</t>
+          <t>-22,32; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1029,22 +1029,22 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,96; 0,0</t>
+          <t>-36,41; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-76,27; 0,0</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 48,18</t>
+          <t>-17,89; 64,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 65,28</t>
+          <t>-28,5; 54,59</t>
         </is>
       </c>
     </row>
@@ -1099,17 +1099,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-29,59; 31,2</t>
+          <t>-29,16; 34,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 27,13</t>
+          <t>-29,37; 24,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-69,94; 0,0</t>
+          <t>-70,56; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-33,67; 8,91</t>
+          <t>-36,71; 6,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,77; 13,5</t>
+          <t>-18,0; 13,23</t>
         </is>
       </c>
     </row>
@@ -1175,17 +1175,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,29; 49,55</t>
+          <t>-30,2; 54,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-28,89; 42,32</t>
+          <t>-30,15; 36,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-69,94; 0,0</t>
+          <t>-70,56; 0,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,82; 9,64</t>
+          <t>-38,93; 6,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 16,04</t>
+          <t>-18,27; 16,0</t>
         </is>
       </c>
     </row>
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-48,82; 57,83</t>
+          <t>-52,1; 49,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,0</t>
+          <t>0,0; 80,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-33,63; 49,45</t>
+          <t>-33,85; 48,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,0</t>
+          <t>0,0; 61,6</t>
         </is>
       </c>
     </row>
@@ -1341,29 +1341,29 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-55,08; 229,31</t>
+          <t>-54,85; 140,25</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 300,0</t>
+          <t>0,0; inf</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-34,12; 135,7</t>
+          <t>-34,86; 119,07</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 400,0</t>
+          <t>0,0; 160,38</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1411,17 +1411,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,76</t>
+          <t>0,0; 56,71</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 38,44</t>
+          <t>-100,0; 27,77</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 83,8</t>
+          <t>-2,97; 83,1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,93; 52,75</t>
+          <t>1,05; 53,91</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-84,8; 36,53</t>
+          <t>-84,75; 39,77</t>
         </is>
       </c>
     </row>
@@ -1487,17 +1487,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,69</t>
+          <t>0,0; 131,0</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 62,91</t>
+          <t>-100,0; 38,38</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 514,86</t>
+          <t>-3,71; 494,07</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1507,19 +1507,19 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,07; 115,79</t>
+          <t>1,16; 126,27</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 61,19</t>
+          <t>-100,0; 76,24</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-40,24; 16,35</t>
+          <t>-39,12; 15,36</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-53,38; 6,44</t>
+          <t>-51,57; 11,08</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,17</t>
+          <t>0,0; 47,31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-42,76; 20,17</t>
+          <t>-42,43; 20,6</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-24,16; 11,08</t>
+          <t>-24,18; 11,24</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-40,44; 5,17</t>
+          <t>-40,03; 4,45</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-42,79; 23,44</t>
+          <t>-41,8; 22,39</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-60,12; 6,81</t>
+          <t>-58,05; 14,45</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,53</t>
+          <t>0,0; 89,8</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-47,47; 25,26</t>
+          <t>-46,25; 26,12</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-27,9; 13,51</t>
+          <t>-27,06; 14,22</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-44,56; 6,62</t>
+          <t>-44,89; 5,85</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-25,76; 50,67</t>
+          <t>-23,92; 55,04</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>20,11; 71,96</t>
+          <t>19,82; 71,68</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-32,36; 13,29</t>
+          <t>-30,65; 16,58</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 23,65</t>
+          <t>-11,66; 23,05</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-21,58; 19,84</t>
+          <t>-21,69; 21,82</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9,85; 37,28</t>
+          <t>9,73; 36,26</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-36,7; 154,1</t>
+          <t>-34,36; 186,55</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>24,93; 256,3</t>
+          <t>24,72; 251,61</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-36,23; 15,47</t>
+          <t>-33,34; 20,35</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 31,38</t>
+          <t>-11,9; 30,58</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-25,42; 29,09</t>
+          <t>-26,24; 32,98</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,67; 60,27</t>
+          <t>11,58; 57,28</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 13,85</t>
+          <t>-10,37; 14,61</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 15,17</t>
+          <t>-9,19; 15,33</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 8,45</t>
+          <t>-10,59; 8,02</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 11,43</t>
+          <t>-6,62; 11,3</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 6,78</t>
+          <t>-8,88; 6,55</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 9,32</t>
+          <t>-6,65; 8,3</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 19,7</t>
+          <t>-11,89; 21,32</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 21,35</t>
+          <t>-10,72; 21,07</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 9,86</t>
+          <t>-11,32; 9,73</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 13,8</t>
+          <t>-7,05; 13,79</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 8,24</t>
+          <t>-9,8; 8,24</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 11,44</t>
+          <t>-7,56; 10,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B02-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16B02-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-33,26; 0,0</t>
+          <t>-36,01; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-65,26; -7,71</t>
+          <t>-56,59; -7,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-39,83; 0,0</t>
+          <t>-34,66; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-37,18; 0,0</t>
+          <t>-36,94; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 0,0</t>
+          <t>-23,38; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-38,98; -7,51</t>
+          <t>-40,43; -7,24</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,26; 0,0</t>
+          <t>-36,01; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-65,26; -7,71</t>
+          <t>-56,59; -7,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-39,83; 0,0</t>
+          <t>-34,66; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-37,18; 0,0</t>
+          <t>-36,94; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 0,0</t>
+          <t>-23,38; 0,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,98; -7,51</t>
+          <t>-40,43; -7,24</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-38,1; -4,45</t>
+          <t>-39,54; -4,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-34,84; 0,0</t>
+          <t>-35,22; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-28,25; -3,57</t>
+          <t>-29,55; -3,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,9; -6,02</t>
+          <t>-26,1; -6,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 0,0</t>
+          <t>-16,48; 0,0</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,1; -4,45</t>
+          <t>-39,54; -4,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-34,84; 0,0</t>
+          <t>-35,22; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,25; -3,57</t>
+          <t>-29,55; -3,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,9; -6,02</t>
+          <t>-26,1; -6,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 0,0</t>
+          <t>-16,48; 0,0</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-22,3; 93,39</t>
+          <t>-21,44; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-36,41; 0,0</t>
+          <t>-30,38; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-76,27; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,72; 36,84</t>
+          <t>-17,2; 34,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,43; 34,99</t>
+          <t>-22,32; 43,66</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-22,32; —</t>
+          <t>-21,67; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1029,22 +1029,22 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,41; 0,0</t>
+          <t>-30,38; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-76,27; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 64,09</t>
+          <t>-17,59; 50,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-28,5; 54,59</t>
+          <t>-24,26; 68,55</t>
         </is>
       </c>
     </row>
@@ -1099,17 +1099,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-29,16; 34,52</t>
+          <t>-29,65; 28,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-29,37; 24,99</t>
+          <t>-27,12; 31,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-70,56; 0,0</t>
+          <t>-69,12; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 6,18</t>
+          <t>-34,94; 6,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,0; 13,23</t>
+          <t>-18,52; 12,12</t>
         </is>
       </c>
     </row>
@@ -1175,17 +1175,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,2; 54,95</t>
+          <t>-30,67; 44,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,15; 36,52</t>
+          <t>-28,44; 44,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,56; 0,0</t>
+          <t>-69,12; 0,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,93; 6,06</t>
+          <t>-36,23; 6,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 16,0</t>
+          <t>-19,45; 13,73</t>
         </is>
       </c>
     </row>
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-52,1; 49,9</t>
+          <t>-46,32; 58,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,48</t>
+          <t>0,0; 75,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-33,85; 48,92</t>
+          <t>-33,37; 54,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,6</t>
+          <t>0,0; 80,0</t>
         </is>
       </c>
     </row>
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-54,85; 140,25</t>
+          <t>-52,64; 229,67</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,0; inf</t>
+          <t>0,0; 300,0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-34,86; 119,07</t>
+          <t>-33,91; 207,18</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 160,38</t>
+          <t>0,0; 400,0</t>
         </is>
       </c>
     </row>
@@ -1411,17 +1411,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,71</t>
+          <t>0,0; 42,77</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 27,77</t>
+          <t>-100,0; 27,67</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 83,1</t>
+          <t>-2,08; 83,91</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,05; 53,91</t>
+          <t>1,15; 53,83</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-84,75; 39,77</t>
+          <t>-78,74; 30,55</t>
         </is>
       </c>
     </row>
@@ -1487,17 +1487,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0,0; 131,0</t>
+          <t>0,0; 74,73</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 38,38</t>
+          <t>-100,0; 38,14</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 494,07</t>
+          <t>-2,73; 521,05</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1507,12 +1507,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,16; 126,27</t>
+          <t>1,3; 133,06</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 76,24</t>
+          <t>-100,0; 61,18</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-39,12; 15,36</t>
+          <t>-41,59; 15,19</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-51,57; 11,08</t>
+          <t>-52,51; 8,19</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,31</t>
+          <t>0,0; 40,73</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-42,43; 20,6</t>
+          <t>-44,65; 20,08</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-24,18; 11,24</t>
+          <t>-25,16; 13,63</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-40,03; 4,45</t>
+          <t>-40,38; 5,82</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-41,8; 22,39</t>
+          <t>-45,46; 20,66</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-58,05; 14,45</t>
+          <t>-59,01; 6,65</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0,0; 89,8</t>
+          <t>0,0; 68,71</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-46,25; 26,12</t>
+          <t>-48,33; 25,11</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-27,06; 14,22</t>
+          <t>-27,9; 16,38</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-44,89; 5,85</t>
+          <t>-45,74; 6,12</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-23,92; 55,04</t>
+          <t>-26,27; 52,05</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>19,82; 71,68</t>
+          <t>20,07; 71,82</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-30,65; 16,58</t>
+          <t>-30,88; 14,87</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 23,05</t>
+          <t>-9,57; 23,35</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 21,82</t>
+          <t>-18,97; 20,92</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9,73; 36,26</t>
+          <t>8,43; 35,61</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-34,36; 186,55</t>
+          <t>-39,86; 162,98</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>24,72; 251,61</t>
+          <t>25,11; 254,72</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-33,34; 20,35</t>
+          <t>-34,01; 18,19</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 30,58</t>
+          <t>-9,94; 30,6</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-26,24; 32,98</t>
+          <t>-22,76; 31,74</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,58; 57,28</t>
+          <t>9,63; 59,53</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 14,61</t>
+          <t>-10,93; 14,12</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 15,33</t>
+          <t>-9,26; 15,93</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 8,02</t>
+          <t>-9,97; 8,22</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 11,3</t>
+          <t>-7,17; 10,94</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 6,55</t>
+          <t>-8,29; 5,95</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 8,3</t>
+          <t>-5,57; 8,88</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 21,32</t>
+          <t>-12,71; 19,88</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 21,07</t>
+          <t>-10,58; 22,07</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 9,73</t>
+          <t>-10,94; 9,68</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 13,79</t>
+          <t>-7,7; 13,1</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 8,24</t>
+          <t>-9,23; 7,29</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 10,25</t>
+          <t>-6,24; 10,92</t>
         </is>
       </c>
     </row>
